--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484807_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484807_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.747299999999999</v>
+        <v>7.8737</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4655</v>
+        <v>8.803599999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.7181999999999999</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>4.3887</v>
@@ -610,13 +610,13 @@
         <v>1.1322</v>
       </c>
       <c r="S2" t="n">
-        <v>3.1133</v>
+        <v>2.2397</v>
       </c>
       <c r="T2" t="n">
-        <v>2.2237</v>
+        <v>1.5618</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8895</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.3018</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7889</v>
+        <v>2.6323</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5762</v>
+        <v>1.4989</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2127</v>
+        <v>1.1334</v>
       </c>
       <c r="G3" t="n">
         <v>1.5797</v>
@@ -688,13 +688,13 @@
         <v>0.7548</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4544</v>
+        <v>0.2977</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1205</v>
+        <v>0.0432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3339</v>
+        <v>0.2546</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>V. AVIÑO ESPAÑA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8552</v>
+        <v>0.6339</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9508</v>
+        <v>0.6339</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0956</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5273</v>
+        <v>0.6339</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7239</v>
+        <v>0.6339</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1966</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.945</v>
+        <v>0.6339</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9039</v>
+        <v>0.6339</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0411</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4177</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.18</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.2377</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7548</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1322</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7053</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>1.8928</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1875</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.6226</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>V. AVIÑO ESPAÑA</t>
+          <t>A. DOMINGUEZ CARRAL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6339</v>
+        <v>0.4103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6339</v>
+        <v>2.562</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-2.1517</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6339</v>
+        <v>1.2347</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6339</v>
+        <v>1.3085</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.0737</v>
       </c>
       <c r="J6" t="n">
-        <v>0.6339</v>
+        <v>2.1883</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6339</v>
+        <v>1.5698</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.6183999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>-0.9535</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.2614</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.6922</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>0.5661</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1322</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.6983</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.4207</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.2231</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>0.1976</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-2.8112</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2828</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.094</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. DOMINGUEZ CARRAL</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3411</v>
+        <v>0.0694</v>
       </c>
       <c r="E7" t="n">
-        <v>2.6779</v>
+        <v>0.1915</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3368</v>
+        <v>-0.122</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2347</v>
+        <v>0.5273</v>
       </c>
       <c r="H7" t="n">
-        <v>1.3085</v>
+        <v>0.7239</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0737</v>
+        <v>-0.1966</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1883</v>
+        <v>0.945</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5698</v>
+        <v>0.9039</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6183999999999999</v>
+        <v>0.0411</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.9535</v>
+        <v>-0.4177</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2614</v>
+        <v>-0.18</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6922</v>
+        <v>-0.2377</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5661</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1322</v>
+        <v>-1.887</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6983</v>
+        <v>1.1322</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3515</v>
+        <v>0.9195</v>
       </c>
       <c r="T7" t="n">
-        <v>1.339</v>
+        <v>1.1335</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0124</v>
+        <v>-0.2139</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.8112</v>
+        <v>-0.6226</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2828</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.094</v>
+        <v>-0.6226</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>V. AVINO ESPANA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8209</v>
+        <v>-0.8638</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0469</v>
+        <v>-0.0433</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.774</v>
+        <v>-0.8205</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.9382</v>
+        <v>-1.524</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.5921</v>
+        <v>0.0611</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3461</v>
+        <v>-1.585</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.3297</v>
+        <v>-1.1553</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.1523</v>
+        <v>0.1268</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8226</v>
+        <v>-1.2821</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.6085</v>
+        <v>-0.3687</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4398</v>
+        <v>-0.06569999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1687</v>
+        <v>-0.303</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.1322</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1322</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>1.1322</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5513</v>
+        <v>-0.1702</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9246</v>
+        <v>-0.1332</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6267</v>
+        <v>-0.037</v>
       </c>
       <c r="V8" t="n">
-        <v>1.566</v>
+        <v>-0.3018</v>
       </c>
       <c r="W8" t="n">
-        <v>2.4904</v>
+        <v>1.2452</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.9244</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. AVINO ESPANA</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9981</v>
+        <v>-0.9698</v>
       </c>
       <c r="E9" t="n">
-        <v>0.034</v>
+        <v>0.4221</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0321</v>
+        <v>-1.3919</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.524</v>
+        <v>0.0086</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0611</v>
+        <v>1.9111</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.585</v>
+        <v>-1.9025</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.1553</v>
+        <v>2.0289</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1268</v>
+        <v>2.5465</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2821</v>
+        <v>-0.5177</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3687</v>
+        <v>-2.0203</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.6354</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.303</v>
+        <v>-1.3848</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1322</v>
+        <v>-2.4531</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.9627</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1322</v>
+        <v>1.5096</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3045</v>
+        <v>1.8144</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0559</v>
+        <v>1.4504</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2486</v>
+        <v>0.364</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3018</v>
+        <v>-0.3398</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2452</v>
+        <v>0.9054</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.547</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.09</v>
+        <v>-1.0305</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2801</v>
+        <v>-0.1242</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8099</v>
+        <v>-0.9063</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0086</v>
+        <v>-3.9382</v>
       </c>
       <c r="H10" t="n">
-        <v>1.9111</v>
+        <v>-3.5921</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9025</v>
+        <v>-0.3461</v>
       </c>
       <c r="J10" t="n">
-        <v>2.0289</v>
+        <v>-2.3297</v>
       </c>
       <c r="K10" t="n">
-        <v>2.5465</v>
+        <v>-3.1523</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5177</v>
+        <v>0.8226</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0203</v>
+        <v>-1.6085</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6354</v>
+        <v>-0.4398</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3848</v>
+        <v>-1.1687</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.4531</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.9627</v>
+        <v>-1.1322</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5096</v>
+        <v>1.1322</v>
       </c>
       <c r="S10" t="n">
-        <v>1.6942</v>
+        <v>1.3418</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7483</v>
+        <v>0.8473000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.946</v>
+        <v>0.4944</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3398</v>
+        <v>1.566</v>
       </c>
       <c r="W10" t="n">
-        <v>0.9054</v>
+        <v>2.4904</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2452</v>
+        <v>-0.9244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. ALEMANY GARCIA</t>
+          <t>I. HORRACH SANCHEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6777</v>
+        <v>-3.2874</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4686</v>
+        <v>-0.9484</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2092</v>
+        <v>-2.339</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.874</v>
+        <v>0.2933</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.5793</v>
+        <v>0.4383</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.2948</v>
+        <v>-0.145</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.4715</v>
+        <v>1.6905</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.1723</v>
+        <v>0.4069</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2991</v>
+        <v>1.2836</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.4026</v>
+        <v>-1.3972</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4069</v>
+        <v>0.0313</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.9956</v>
+        <v>-1.4285</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3774</v>
+        <v>-2.0757</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9435</v>
+        <v>-2.8305</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5661</v>
+        <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5737</v>
+        <v>-0.2598</v>
       </c>
       <c r="T11" t="n">
-        <v>0.9464</v>
+        <v>0.1916</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3727</v>
+        <v>-0.4514</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. HORRACH SANCHEZ</t>
+          <t>F. ALEMANY GARCIA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.1257</v>
+        <v>-3.6429</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7867</v>
+        <v>-2.566</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.339</v>
+        <v>-1.0769</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2933</v>
+        <v>-3.874</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4383</v>
+        <v>-1.5793</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.145</v>
+        <v>-2.2948</v>
       </c>
       <c r="J12" t="n">
-        <v>1.6905</v>
+        <v>-2.4715</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4069</v>
+        <v>-1.1723</v>
       </c>
       <c r="L12" t="n">
-        <v>1.2836</v>
+        <v>-1.2991</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.3972</v>
+        <v>-1.4026</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0313</v>
+        <v>-0.4069</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.4285</v>
+        <v>-0.9956</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0757</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.8305</v>
+        <v>-0.9435</v>
       </c>
       <c r="R12" t="n">
-        <v>0.7548</v>
+        <v>0.5661</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0981</v>
+        <v>0.6086</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.849</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4514</v>
+        <v>-0.2404</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.4642</v>
+        <v>-8.4597</v>
       </c>
       <c r="E13" t="n">
-        <v>-10.1918</v>
+        <v>-8.69</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2723</v>
+        <v>0.2303</v>
       </c>
       <c r="G13" t="n">
         <v>-5.3266</v>
@@ -1468,13 +1468,13 @@
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1375</v>
+        <v>0.8669</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8448</v>
+        <v>0.657</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2927</v>
+        <v>0.2099</v>
       </c>
       <c r="V13" t="n">
         <v>-1.547</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-6.2424</v>
+        <v>-5.066699999999998</v>
       </c>
       <c r="E14" t="n">
-        <v>2.132</v>
+        <v>3.307899999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-8.3744</v>
+        <v>-8.374499999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-4.428800000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>4.554900000000001</v>
+        <v>4.5549</v>
       </c>
       <c r="I14" t="n">
         <v>-8.9833</v>
@@ -1528,7 +1528,7 @@
         <v>-2.6009</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.481399999999999</v>
+        <v>-9.481400000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-3.0989</v>
@@ -1546,19 +1546,19 @@
         <v>11.322</v>
       </c>
       <c r="S14" t="n">
-        <v>7.9036</v>
+        <v>9.0793</v>
       </c>
       <c r="T14" t="n">
-        <v>6.6479</v>
+        <v>7.823700000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2556</v>
+        <v>1.2557</v>
       </c>
       <c r="V14" t="n">
         <v>-4.9998</v>
       </c>
       <c r="W14" t="n">
-        <v>6.470800000000001</v>
+        <v>6.4708</v>
       </c>
       <c r="X14" t="n">
         <v>-11.4706</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4375</v>
+        <v>5.881</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7385</v>
+        <v>6.7129</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.301</v>
+        <v>-0.8319</v>
       </c>
       <c r="G15" t="n">
         <v>3.3621</v>
@@ -1624,13 +1624,13 @@
         <v>3.0192</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.66</v>
+        <v>-1.2166</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.5626</v>
+        <v>-0.5881999999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.0974</v>
+        <v>-0.6283</v>
       </c>
       <c r="V15" t="n">
         <v>4.679</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. BLEDA MIRANDA</t>
+          <t>F. ALBERT ABELLAN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.3905</v>
+        <v>2.5637</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2428</v>
+        <v>2.564</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1478</v>
+        <v>-0.0004</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1082</v>
+        <v>-1.2683</v>
       </c>
       <c r="H16" t="n">
-        <v>2.4973</v>
+        <v>-0.8976</v>
       </c>
       <c r="I16" t="n">
-        <v>0.611</v>
+        <v>-0.3707</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0392</v>
+        <v>-0.1494</v>
       </c>
       <c r="K16" t="n">
-        <v>2.7101</v>
+        <v>0.8929</v>
       </c>
       <c r="L16" t="n">
-        <v>0.329</v>
+        <v>-1.0424</v>
       </c>
       <c r="M16" t="n">
-        <v>0.06909999999999999</v>
+        <v>-1.1189</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2128</v>
+        <v>-1.7905</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2819</v>
+        <v>0.6717</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.9435</v>
+        <v>2.6418</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.0192</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0757</v>
+        <v>2.8305</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5466</v>
+        <v>-1.621</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2608</v>
+        <v>-0.2108</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2858</v>
+        <v>-1.4102</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.3208</v>
+        <v>2.8112</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.038</v>
+        <v>3.113</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2828</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="17">
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. ALBERT ABELLAN</t>
+          <t>C. BLEDA MIRANDA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.0602</v>
+        <v>2.2941</v>
       </c>
       <c r="E18" t="n">
-        <v>1.9794</v>
+        <v>0.3915</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9192</v>
+        <v>1.9026</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.2683</v>
+        <v>3.1082</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.8976</v>
+        <v>2.4973</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.3707</v>
+        <v>0.611</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1494</v>
+        <v>3.0392</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8929</v>
+        <v>2.7101</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.0424</v>
+        <v>0.329</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1189</v>
+        <v>0.06909999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.7905</v>
+        <v>-0.2128</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6717</v>
+        <v>0.2819</v>
       </c>
       <c r="P18" t="n">
-        <v>2.6418</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.1887</v>
+        <v>-3.0192</v>
       </c>
       <c r="R18" t="n">
-        <v>2.8305</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>-3.1244</v>
+        <v>0.4502</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7955</v>
+        <v>0.4095</v>
       </c>
       <c r="U18" t="n">
-        <v>-2.329</v>
+        <v>0.0407</v>
       </c>
       <c r="V18" t="n">
-        <v>2.8112</v>
+        <v>-0.3208</v>
       </c>
       <c r="W18" t="n">
-        <v>3.113</v>
+        <v>-0.038</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3018</v>
+        <v>-0.2828</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FEDOROV</t>
+          <t>J. MUNOZ PALENCIA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1281</v>
+        <v>0.1313</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3697</v>
+        <v>-0.3759</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2417</v>
+        <v>0.5072</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0683</v>
+        <v>-2.0297</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6073</v>
+        <v>-2.9817</v>
       </c>
       <c r="I19" t="n">
-        <v>0.4609</v>
+        <v>0.952</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5874</v>
+        <v>-0.2612</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3647</v>
+        <v>-1.0612</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2227</v>
+        <v>0.8</v>
       </c>
       <c r="M19" t="n">
-        <v>0.4809</v>
+        <v>-1.7684</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2426</v>
+        <v>-1.9205</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2383</v>
+        <v>0.152</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3774</v>
+        <v>1.887</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3209</v>
+        <v>3.0192</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5502</v>
+        <v>-1.273</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7259</v>
+        <v>-0.5295</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.1757</v>
+        <v>-0.7435</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.8678</v>
+        <v>1.547</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.547</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.8678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0233</v>
+        <v>-0.2329</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2874</v>
+        <v>0.19</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2641</v>
+        <v>-0.4228</v>
       </c>
       <c r="G20" t="n">
         <v>-0.8334</v>
@@ -2014,13 +2014,13 @@
         <v>1.1322</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2945</v>
+        <v>-0.5507</v>
       </c>
       <c r="T20" t="n">
-        <v>0.074</v>
+        <v>-0.0234</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3685</v>
+        <v>-0.5273</v>
       </c>
       <c r="V20" t="n">
         <v>0.019</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. MUNOZ PALENCIA</t>
+          <t>K. FEDOROV</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2857</v>
+        <v>-0.3039</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3502</v>
+        <v>0.4928</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0646</v>
+        <v>-0.7967</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0297</v>
+        <v>1.0683</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.9817</v>
+        <v>0.6073</v>
       </c>
       <c r="I21" t="n">
-        <v>0.952</v>
+        <v>0.4609</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.2612</v>
+        <v>0.5874</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.0612</v>
+        <v>0.3647</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8</v>
+        <v>0.2227</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7684</v>
+        <v>0.4809</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9205</v>
+        <v>0.2426</v>
       </c>
       <c r="O21" t="n">
-        <v>0.152</v>
+        <v>0.2383</v>
       </c>
       <c r="P21" t="n">
-        <v>1.887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R21" t="n">
-        <v>3.0192</v>
+        <v>1.3209</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.69</v>
+        <v>0.1183</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5038</v>
+        <v>0.849</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1862</v>
+        <v>-0.7307</v>
       </c>
       <c r="V21" t="n">
-        <v>1.547</v>
+        <v>-1.8678</v>
       </c>
       <c r="W21" t="n">
-        <v>1.547</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.8678</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4748</v>
+        <v>-1.5987</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4164</v>
+        <v>-1.5139</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0583</v>
+        <v>-0.0848</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8956</v>
@@ -2170,13 +2170,13 @@
         <v>1.1322</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2775</v>
+        <v>-0.4013</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2199</v>
+        <v>-0.3173</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0575</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2452</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5385</v>
+        <v>-3.0453</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.9785</v>
+        <v>-2.5887</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.4566</v>
       </c>
       <c r="G23" t="n">
         <v>-0.5845</v>
@@ -2248,13 +2248,13 @@
         <v>1.5096</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.954</v>
+        <v>-1.4608</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.2345</v>
+        <v>-0.8448</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7194</v>
+        <v>-0.616</v>
       </c>
       <c r="V23" t="n">
         <v>-0.6226</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>6.242299999999999</v>
+        <v>8.190999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>8.374399999999998</v>
+        <v>8.374400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.1319</v>
+        <v>-0.1833999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>4.428799999999999</v>
@@ -2299,10 +2299,10 @@
         <v>8.9833</v>
       </c>
       <c r="J24" t="n">
-        <v>9.4816</v>
+        <v>9.481600000000002</v>
       </c>
       <c r="K24" t="n">
-        <v>3.098900000000001</v>
+        <v>3.0989</v>
       </c>
       <c r="L24" t="n">
         <v>6.3825</v>
@@ -2326,13 +2326,13 @@
         <v>16.0395</v>
       </c>
       <c r="S24" t="n">
-        <v>-7.9036</v>
+        <v>-5.954899999999999</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.2556</v>
+        <v>-1.2555</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.6479</v>
+        <v>-4.699299999999999</v>
       </c>
       <c r="V24" t="n">
         <v>4.999799999999999</v>
